--- a/results/detailed_report_vem1.xlsx
+++ b/results/detailed_report_vem1.xlsx
@@ -473,13 +473,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>2.191749782308396e-11</v>
+        <v>2.191749595569285e-11</v>
       </c>
       <c r="E2" t="n">
         <v>59</v>
       </c>
       <c r="F2" t="n">
-        <v>0.1175971000002392</v>
+        <v>0.03533400000014808</v>
       </c>
     </row>
     <row r="3">
@@ -495,13 +495,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>3.508245312705718e-09</v>
+        <v>3.508245363805012e-09</v>
       </c>
       <c r="E3" t="n">
         <v>2338</v>
       </c>
       <c r="F3" t="n">
-        <v>19.17345579999983</v>
+        <v>10.50097770000139</v>
       </c>
     </row>
     <row r="4">
@@ -517,13 +517,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>2.71316976420256e-09</v>
+        <v>2.71316985146645e-09</v>
       </c>
       <c r="E4" t="n">
         <v>3058</v>
       </c>
       <c r="F4" t="n">
-        <v>6.170415600000524</v>
+        <v>1.486297100000229</v>
       </c>
     </row>
     <row r="5">
@@ -539,13 +539,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>3.539460317815586e-09</v>
+        <v>3.53946035755399e-09</v>
       </c>
       <c r="E5" t="n">
         <v>4671</v>
       </c>
       <c r="F5" t="n">
-        <v>100.2428377000006</v>
+        <v>76.96998689999964</v>
       </c>
     </row>
     <row r="6">
@@ -561,13 +561,13 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>2.831873382000351e-09</v>
+        <v>2.831873384016187e-09</v>
       </c>
       <c r="E6" t="n">
         <v>53</v>
       </c>
       <c r="F6" t="n">
-        <v>0.1108796999997139</v>
+        <v>0.0397486999972898</v>
       </c>
     </row>
     <row r="7">
@@ -583,13 +583,13 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>3.517457026261615e-07</v>
+        <v>3.517457026265609e-07</v>
       </c>
       <c r="E7" t="n">
         <v>1778</v>
       </c>
       <c r="F7" t="n">
-        <v>14.7313022999997</v>
+        <v>11.75299710000036</v>
       </c>
     </row>
     <row r="8">
@@ -605,13 +605,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>2.695337418308125e-07</v>
+        <v>2.695337419180719e-07</v>
       </c>
       <c r="E8" t="n">
         <v>2336</v>
       </c>
       <c r="F8" t="n">
-        <v>4.731017400000383</v>
+        <v>1.735977200001798</v>
       </c>
     </row>
     <row r="9">
@@ -627,13 +627,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>3.539765973113712e-07</v>
+        <v>3.539765973220114e-07</v>
       </c>
       <c r="E9" t="n">
         <v>3552</v>
       </c>
       <c r="F9" t="n">
-        <v>77.73989590000019</v>
+        <v>59.62504040000204</v>
       </c>
     </row>
     <row r="10">
@@ -649,13 +649,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>3.732339701535603e-07</v>
+        <v>3.732339701465672e-07</v>
       </c>
       <c r="E10" t="n">
         <v>45</v>
       </c>
       <c r="F10" t="n">
-        <v>0.09903960000065126</v>
+        <v>0.02119970000057947</v>
       </c>
     </row>
     <row r="11">
@@ -671,13 +671,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>3.526696849704469e-05</v>
+        <v>3.526696849704578e-05</v>
       </c>
       <c r="E11" t="n">
         <v>1218</v>
       </c>
       <c r="F11" t="n">
-        <v>10.75422400000025</v>
+        <v>6.956799100000353</v>
       </c>
     </row>
     <row r="12">
@@ -693,13 +693,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>2.713339183797155e-05</v>
+        <v>2.713339183805879e-05</v>
       </c>
       <c r="E12" t="n">
         <v>1612</v>
       </c>
       <c r="F12" t="n">
-        <v>3.469268499999998</v>
+        <v>1.025593599999411</v>
       </c>
     </row>
     <row r="13">
@@ -715,13 +715,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>3.540073343178274e-05</v>
+        <v>3.540073343179866e-05</v>
       </c>
       <c r="E13" t="n">
         <v>2433</v>
       </c>
       <c r="F13" t="n">
-        <v>51.44029140000021</v>
+        <v>36.26640920000136</v>
       </c>
     </row>
     <row r="14">
@@ -737,13 +737,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>4.08279315868696e-05</v>
+        <v>4.082793158685096e-05</v>
       </c>
       <c r="E14" t="n">
         <v>38</v>
       </c>
       <c r="F14" t="n">
-        <v>0.08143239999935759</v>
+        <v>0.01949299999978393</v>
       </c>
     </row>
     <row r="15">
@@ -759,13 +759,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>0.003506972597039507</v>
+        <v>0.003506972597039514</v>
       </c>
       <c r="E15" t="n">
         <v>659</v>
       </c>
       <c r="F15" t="n">
-        <v>5.435533099999702</v>
+        <v>3.72802529999899</v>
       </c>
     </row>
     <row r="16">
@@ -781,13 +781,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>0.002704572409369922</v>
+        <v>0.002704572409369992</v>
       </c>
       <c r="E16" t="n">
         <v>890</v>
       </c>
       <c r="F16" t="n">
-        <v>1.790136100000382</v>
+        <v>0.4965947999990021</v>
       </c>
     </row>
     <row r="17">
@@ -803,13 +803,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>0.003540380757410241</v>
+        <v>0.003540380757410261</v>
       </c>
       <c r="E17" t="n">
         <v>1314</v>
       </c>
       <c r="F17" t="n">
-        <v>27.17454050000015</v>
+        <v>19.61297019999984</v>
       </c>
     </row>
   </sheetData>

--- a/results/detailed_report_vem1.xlsx
+++ b/results/detailed_report_vem1.xlsx
@@ -479,7 +479,7 @@
         <v>59</v>
       </c>
       <c r="F2" t="n">
-        <v>0.03533400000014808</v>
+        <v>0.04878690000077768</v>
       </c>
     </row>
     <row r="3">
@@ -501,7 +501,7 @@
         <v>2338</v>
       </c>
       <c r="F3" t="n">
-        <v>10.50097770000139</v>
+        <v>13.40626690000136</v>
       </c>
     </row>
     <row r="4">
@@ -523,7 +523,7 @@
         <v>3058</v>
       </c>
       <c r="F4" t="n">
-        <v>1.486297100000229</v>
+        <v>2.153369300000122</v>
       </c>
     </row>
     <row r="5">
@@ -545,7 +545,7 @@
         <v>4671</v>
       </c>
       <c r="F5" t="n">
-        <v>76.96998689999964</v>
+        <v>78.42550999999912</v>
       </c>
     </row>
     <row r="6">
@@ -567,7 +567,7 @@
         <v>53</v>
       </c>
       <c r="F6" t="n">
-        <v>0.0397486999972898</v>
+        <v>0.03152450000015961</v>
       </c>
     </row>
     <row r="7">
@@ -589,7 +589,7 @@
         <v>1778</v>
       </c>
       <c r="F7" t="n">
-        <v>11.75299710000036</v>
+        <v>12.1757362999997</v>
       </c>
     </row>
     <row r="8">
@@ -611,7 +611,7 @@
         <v>2336</v>
       </c>
       <c r="F8" t="n">
-        <v>1.735977200001798</v>
+        <v>1.479759200001354</v>
       </c>
     </row>
     <row r="9">
@@ -633,7 +633,7 @@
         <v>3552</v>
       </c>
       <c r="F9" t="n">
-        <v>59.62504040000204</v>
+        <v>61.06195549999939</v>
       </c>
     </row>
     <row r="10">
@@ -655,7 +655,7 @@
         <v>45</v>
       </c>
       <c r="F10" t="n">
-        <v>0.02119970000057947</v>
+        <v>0.03992409999955271</v>
       </c>
     </row>
     <row r="11">
@@ -677,7 +677,7 @@
         <v>1218</v>
       </c>
       <c r="F11" t="n">
-        <v>6.956799100000353</v>
+        <v>11.71900230000028</v>
       </c>
     </row>
     <row r="12">
@@ -699,7 +699,7 @@
         <v>1612</v>
       </c>
       <c r="F12" t="n">
-        <v>1.025593599999411</v>
+        <v>1.545260099999723</v>
       </c>
     </row>
     <row r="13">
@@ -721,7 +721,7 @@
         <v>2433</v>
       </c>
       <c r="F13" t="n">
-        <v>36.26640920000136</v>
+        <v>44.20116360000065</v>
       </c>
     </row>
     <row r="14">
@@ -743,7 +743,7 @@
         <v>38</v>
       </c>
       <c r="F14" t="n">
-        <v>0.01949299999978393</v>
+        <v>0.02330839999922318</v>
       </c>
     </row>
     <row r="15">
@@ -765,7 +765,7 @@
         <v>659</v>
       </c>
       <c r="F15" t="n">
-        <v>3.72802529999899</v>
+        <v>3.693872699999702</v>
       </c>
     </row>
     <row r="16">
@@ -787,7 +787,7 @@
         <v>890</v>
       </c>
       <c r="F16" t="n">
-        <v>0.4965947999990021</v>
+        <v>0.5207531000014569</v>
       </c>
     </row>
     <row r="17">
@@ -809,7 +809,7 @@
         <v>1314</v>
       </c>
       <c r="F17" t="n">
-        <v>19.61297019999984</v>
+        <v>22.2550183000003</v>
       </c>
     </row>
   </sheetData>
